--- a/VLOOKUP_HLOOKUP_XLOOKUP.xlsx
+++ b/VLOOKUP_HLOOKUP_XLOOKUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHANU SURYAVANSHI\Desktop\new Excel Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91F01C6-1DDC-4CF9-9FE3-9EB2F0FF4516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FD28E8-FE49-4E6B-9CFD-1C08AA0087EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{0E668913-53B6-4D4E-80DC-A3930A4C74DB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{0E668913-53B6-4D4E-80DC-A3930A4C74DB}"/>
   </bookViews>
   <sheets>
     <sheet name="result" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="102">
   <si>
     <t>Roll No</t>
   </si>
@@ -1002,7 +1002,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1019,6 +1019,12 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1056,6 +1062,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1067,16 +1076,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1504,26 +1503,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D5" s="2" t="s">
@@ -1605,14 +1604,14 @@
         <f>COUNTIF(F6:J6,"&lt;50")</f>
         <v>0</v>
       </c>
-      <c r="R6" s="11" t="s">
+      <c r="R6" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="13"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="15"/>
     </row>
     <row r="7" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D7" s="1">
@@ -1656,12 +1655,12 @@
         <f t="shared" ref="O7:O55" si="3">COUNTIF(F7:J7,"&lt;50")</f>
         <v>0</v>
       </c>
-      <c r="R7" s="14"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="17"/>
+      <c r="W7" s="18"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D8" s="1">
@@ -3898,12 +3897,12 @@
   </cols>
   <sheetData>
     <row r="4" spans="4:19" x14ac:dyDescent="0.3">
-      <c r="O4" s="19" t="s">
+      <c r="O4" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
     </row>
     <row r="5" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D5" s="4" t="s">
@@ -3927,10 +3926,10 @@
       <c r="J5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
     </row>
     <row r="6" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D6" s="4">
@@ -4129,12 +4128,12 @@
       <c r="J12" s="4">
         <v>62</v>
       </c>
-      <c r="O12" s="22" t="s">
+      <c r="O12" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
     </row>
     <row r="13" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D13" s="4">
@@ -4158,10 +4157,10 @@
       <c r="J13" s="4">
         <v>94</v>
       </c>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
     </row>
     <row r="14" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D14" s="4">
@@ -4318,10 +4317,10 @@
       <c r="J18" s="4">
         <v>67</v>
       </c>
-      <c r="N18" s="21" t="s">
+      <c r="N18" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="O18" s="20"/>
+      <c r="O18" s="22"/>
     </row>
     <row r="19" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D19" s="4">
@@ -4345,8 +4344,8 @@
       <c r="J19" s="4">
         <v>52</v>
       </c>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D20" s="4">
@@ -4758,12 +4757,12 @@
       <c r="J33" s="4">
         <v>38</v>
       </c>
-      <c r="N33" s="27" t="s">
+      <c r="N33" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="O33" s="27"/>
-      <c r="P33" s="27"/>
-      <c r="Q33" s="27"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
     </row>
     <row r="34" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D34" s="4">
@@ -4787,10 +4786,10 @@
       <c r="J34" s="4">
         <v>71</v>
       </c>
-      <c r="N34" s="27"/>
-      <c r="O34" s="27"/>
-      <c r="P34" s="27"/>
-      <c r="Q34" s="27"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
     </row>
     <row r="35" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
@@ -4989,12 +4988,12 @@
       <c r="J41" s="4">
         <v>60</v>
       </c>
-      <c r="N41" s="30" t="s">
+      <c r="N41" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="O41" s="30"/>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="30"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
     </row>
     <row r="42" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D42" s="4">
@@ -5018,16 +5017,15 @@
       <c r="J42" s="4">
         <v>75</v>
       </c>
-      <c r="N42" s="29" t="s">
+      <c r="N42" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="30"/>
-      <c r="S42" s="30"/>
-      <c r="T42" s="30"/>
-      <c r="U42" s="28"/>
+      <c r="O42" s="12"/>
+      <c r="P42" s="12"/>
+      <c r="Q42" s="12"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
+      <c r="T42" s="11"/>
     </row>
     <row r="43" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D43" s="4">
@@ -5051,16 +5049,16 @@
       <c r="J43" s="4">
         <v>40</v>
       </c>
-      <c r="N43" s="29" t="s">
+      <c r="N43" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
+      <c r="O43" s="12"/>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="12"/>
+      <c r="R43" s="12"/>
+      <c r="S43" s="12"/>
+      <c r="T43" s="12"/>
+      <c r="U43" s="12"/>
     </row>
     <row r="44" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D44" s="4">
@@ -5084,10 +5082,10 @@
       <c r="J44" s="4">
         <v>69</v>
       </c>
-      <c r="R44" s="29"/>
-      <c r="S44" s="29"/>
-      <c r="T44" s="29"/>
-      <c r="U44" s="29"/>
+      <c r="R44" s="12"/>
+      <c r="S44" s="12"/>
+      <c r="T44" s="12"/>
+      <c r="U44" s="12"/>
     </row>
     <row r="45" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D45" s="4">
@@ -5432,12 +5430,12 @@
       <c r="G2" s="7">
         <v>75</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A3" s="7">
@@ -5461,10 +5459,10 @@
       <c r="G3" s="7">
         <v>82</v>
       </c>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A4" s="7">
@@ -5488,10 +5486,10 @@
       <c r="G4" s="7">
         <v>55</v>
       </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A5" s="7">
@@ -5706,11 +5704,11 @@
       <c r="G10" s="7">
         <v>46</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A11" s="7">
@@ -5734,9 +5732,9 @@
       <c r="G11" s="7">
         <v>72</v>
       </c>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A12" s="7">
@@ -5901,11 +5899,11 @@
       <c r="G17" s="7">
         <v>86</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="7">
@@ -5929,9 +5927,9 @@
       <c r="G18" s="7">
         <v>64</v>
       </c>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="7">
@@ -6746,14 +6744,14 @@
     <col min="6" max="6" width="8.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.88671875" style="5"/>
-    <col min="9" max="9" width="18.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" style="5"/>
+    <col min="9" max="9" width="17.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="5"/>
-    <col min="15" max="15" width="17.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.33203125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
@@ -6832,14 +6830,14 @@
         <f>INDEX(A1:G11,5,4)</f>
         <v>88</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="M3" s="26"/>
-      <c r="O3" s="26" t="s">
+      <c r="M3" s="29"/>
+      <c r="O3" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="P3" s="26"/>
+      <c r="P3" s="29"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="7">
@@ -6863,10 +6861,10 @@
       <c r="G4" s="7">
         <v>55</v>
       </c>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="7">
@@ -6890,10 +6888,10 @@
       <c r="G5" s="7">
         <v>90</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="26"/>
       <c r="K5" s="8"/>
       <c r="M5" s="5" t="s">
         <v>4</v>
@@ -6928,8 +6926,8 @@
       <c r="G6" s="7">
         <v>45</v>
       </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
       <c r="K6" s="8"/>
       <c r="L6" s="5" t="s">
         <v>7</v>
@@ -6968,7 +6966,7 @@
         <v>76</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>9</v>
@@ -7000,11 +6998,11 @@
         <v>62</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J8" s="5">
         <f>INDEX(B1:G51,MATCH(I8,B1:B51,0),MATCH(J7,B1:G1,0))</f>
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="O8" s="7" t="s">
         <v>10</v>
@@ -7093,10 +7091,10 @@
       <c r="G11" s="7">
         <v>72</v>
       </c>
-      <c r="I11" s="26" t="s">
+      <c r="I11" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="29"/>
       <c r="O11" s="7" t="s">
         <v>13</v>
       </c>
@@ -7126,8 +7124,8 @@
       <c r="G12" s="7">
         <v>82</v>
       </c>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
       <c r="O12" s="7" t="s">
         <v>14</v>
       </c>
@@ -7252,7 +7250,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -7274,12 +7272,12 @@
       <c r="G17" s="7">
         <v>86</v>
       </c>
-      <c r="L17" s="26" t="s">
+      <c r="L17" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="M17" s="26"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M17" s="29"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -7301,10 +7299,10 @@
       <c r="G18" s="7">
         <v>64</v>
       </c>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -7330,7 +7328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -7360,7 +7358,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -7383,7 +7381,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -7405,8 +7403,23 @@
       <c r="G22" s="7">
         <v>56</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J22" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A23" s="7">
         <v>22</v>
       </c>
@@ -7428,8 +7441,27 @@
       <c r="G23" s="7">
         <v>85</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="I23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="5" cm="1">
+        <f t="array" ref="J23:N23">_xlfn.XLOOKUP(I23,B2:B51,C2:G51)</f>
+        <v>45</v>
+      </c>
+      <c r="K23" s="5">
+        <v>52</v>
+      </c>
+      <c r="L23" s="5">
+        <v>48</v>
+      </c>
+      <c r="M23" s="5">
+        <v>50</v>
+      </c>
+      <c r="N23" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A24" s="7">
         <v>23</v>
       </c>
@@ -7452,7 +7484,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A25" s="7">
         <v>24</v>
       </c>
@@ -7475,7 +7507,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A26" s="7">
         <v>25</v>
       </c>
@@ -7498,7 +7530,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A27" s="7">
         <v>26</v>
       </c>
@@ -7521,7 +7553,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A28" s="7">
         <v>27</v>
       </c>
@@ -7544,7 +7576,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A29" s="7">
         <v>28</v>
       </c>
@@ -7567,7 +7599,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A30" s="7">
         <v>29</v>
       </c>
@@ -7590,7 +7622,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A31" s="7">
         <v>30</v>
       </c>
@@ -7613,7 +7645,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A32" s="7">
         <v>31</v>
       </c>
@@ -8085,7 +8117,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J7 M5 M19" xr:uid="{DECCFCF7-C88A-4C2B-811F-7E6697450708}">
       <formula1>$C$1:$G$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8 I14 L6 L20" xr:uid="{1F002AC6-2C85-4CDA-8CDA-4FCC69BFE566}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8 I14 L6 L20 I23" xr:uid="{1F002AC6-2C85-4CDA-8CDA-4FCC69BFE566}">
       <formula1>$B$2:$B$51</formula1>
     </dataValidation>
   </dataValidations>
